--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0002T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0002T0006Z000C1N6_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.94625459481048</v>
+        <v>2.266266371656703</v>
       </c>
       <c r="D2" t="n">
-        <v>10.88117746187613</v>
+        <v>1.768191337554871</v>
       </c>
       <c r="E2" t="n">
-        <v>10.33460305067897</v>
+        <v>1.679372995735333</v>
       </c>
       <c r="F2" t="n">
-        <v>15.66396203671999</v>
+        <v>2.545393830966999</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>9.454745904667297</v>
+        <v>1.536396209508436</v>
       </c>
       <c r="D3" t="n">
-        <v>5.681444432151824</v>
+        <v>0.9232347202246713</v>
       </c>
       <c r="E3" t="n">
-        <v>10.33460305067897</v>
+        <v>1.679372995735333</v>
       </c>
       <c r="F3" t="n">
-        <v>15.66396203671999</v>
+        <v>2.545393830966999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.28825281803423</v>
+        <v>4.434341082930564</v>
       </c>
       <c r="D4" t="n">
-        <v>23.85289561075231</v>
+        <v>3.876095536747251</v>
       </c>
       <c r="E4" t="n">
-        <v>10.33460305067897</v>
+        <v>1.679372995735333</v>
       </c>
       <c r="F4" t="n">
-        <v>15.66396203671999</v>
+        <v>2.545393830966999</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.44971034434437</v>
+        <v>3.32307793095596</v>
       </c>
       <c r="D5" t="n">
-        <v>43.04152533601403</v>
+        <v>6.99424786710228</v>
       </c>
       <c r="E5" t="n">
-        <v>10.33460305067897</v>
+        <v>1.679372995735333</v>
       </c>
       <c r="F5" t="n">
-        <v>15.66396203671999</v>
+        <v>2.545393830966999</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.16165072351624</v>
+        <v>3.601268242571389</v>
       </c>
       <c r="D6" t="n">
-        <v>20.57994804946946</v>
+        <v>3.344241558038787</v>
       </c>
       <c r="E6" t="n">
-        <v>10.33460305067897</v>
+        <v>1.679372995735333</v>
       </c>
       <c r="F6" t="n">
-        <v>15.66396203671999</v>
+        <v>2.545393830966999</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.78223635134484</v>
+        <v>5.977113407093537</v>
       </c>
       <c r="D7" t="n">
-        <v>39.98674689028592</v>
+        <v>6.497846369671462</v>
       </c>
       <c r="E7" t="n">
-        <v>10.33460305067897</v>
+        <v>1.679372995735333</v>
       </c>
       <c r="F7" t="n">
-        <v>15.66396203671999</v>
+        <v>2.545393830966999</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.07900281943009</v>
+        <v>5.86283795815739</v>
       </c>
       <c r="D8" t="n">
-        <v>42.08816408181785</v>
+        <v>6.839326663295401</v>
       </c>
       <c r="E8" t="n">
-        <v>10.33460305067897</v>
+        <v>1.679372995735333</v>
       </c>
       <c r="F8" t="n">
-        <v>15.66396203671999</v>
+        <v>2.545393830966999</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>39.08809176753582</v>
+        <v>6.351814912224572</v>
       </c>
       <c r="D9" t="n">
-        <v>51.54479149520181</v>
+        <v>8.376028617970293</v>
       </c>
       <c r="E9" t="n">
-        <v>10.33460305067897</v>
+        <v>1.679372995735333</v>
       </c>
       <c r="F9" t="n">
-        <v>15.66396203671999</v>
+        <v>2.545393830966999</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
